--- a/artfynd/A 28799-2024 artfynd.xlsx
+++ b/artfynd/A 28799-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119506885</v>
+        <v>119506789</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541178</v>
+        <v>541341</v>
       </c>
       <c r="R2" t="n">
-        <v>7246374</v>
+        <v>7246435</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,6 +758,11 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Barksprätt, färska</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -772,14 +782,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>levande, stor gran</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies # levande, stor gran</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119506789</v>
+        <v>119506885</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,39 +818,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541341</v>
+        <v>541178</v>
       </c>
       <c r="R3" t="n">
-        <v>7246435</v>
+        <v>7246374</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,11 +880,6 @@
           <t>2024-08-07</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Barksprätt, färska</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -904,9 +899,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>levande, stor gran</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # levande, stor gran</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -2505,10 +2505,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119506724</v>
+        <v>119506916</v>
       </c>
       <c r="B17" t="n">
-        <v>90905</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2517,41 +2517,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541152</v>
+        <v>541318</v>
       </c>
       <c r="R17" t="n">
-        <v>7246375</v>
+        <v>7246426</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2588,7 +2585,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Kollekt</t>
+          <t>Flera träd</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2597,24 +2594,8 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2631,10 +2612,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119506745</v>
+        <v>119506724</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>90905</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2643,43 +2624,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541139</v>
+        <v>541152</v>
       </c>
       <c r="R18" t="n">
-        <v>7246098</v>
+        <v>7246375</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2716,7 +2695,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack, äldre</t>
+          <t>Kollekt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2725,6 +2704,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2758,7 +2738,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119506742</v>
+        <v>119506745</v>
       </c>
       <c r="B19" t="n">
         <v>57310</v>
@@ -2803,10 +2783,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541246</v>
+        <v>541139</v>
       </c>
       <c r="R19" t="n">
-        <v>7246498</v>
+        <v>7246098</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2843,7 +2823,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, 5 meter upp på stammen</t>
+          <t>Ringhack, äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2885,10 +2865,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119506916</v>
+        <v>119506742</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2901,34 +2881,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541318</v>
+        <v>541246</v>
       </c>
       <c r="R20" t="n">
-        <v>7246426</v>
+        <v>7246498</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2965,7 +2950,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Flera träd</t>
+          <t>Ringhack, äldre, 5 meter upp på stammen</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2976,6 +2961,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">

--- a/artfynd/A 28799-2024 artfynd.xlsx
+++ b/artfynd/A 28799-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119506789</v>
+        <v>119506911</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541341</v>
+        <v>541171</v>
       </c>
       <c r="R2" t="n">
-        <v>7246435</v>
+        <v>7246430</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,11 +753,6 @@
           <t>2024-08-07</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Barksprätt, färska</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -782,9 +772,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Stående, tunn</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Stående, tunn</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119506885</v>
+        <v>119506888</v>
       </c>
       <c r="B3" t="n">
         <v>90580</v>
@@ -842,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541178</v>
+        <v>541357</v>
       </c>
       <c r="R3" t="n">
-        <v>7246374</v>
+        <v>7246528</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,12 +896,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>levande, stor gran</t>
+          <t>Granlåga, tunnare</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies # levande, stor gran</t>
+          <t>Picea abies # Granlåga, tunnare</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -924,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119506918</v>
+        <v>119506892</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,21 +935,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -964,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541357</v>
+        <v>541125</v>
       </c>
       <c r="R4" t="n">
-        <v>7246504</v>
+        <v>7246121</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,6 +1005,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1026,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119506823</v>
+        <v>119506780</v>
       </c>
       <c r="B5" t="n">
-        <v>91005</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,38 +1053,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541301</v>
+        <v>541221</v>
       </c>
       <c r="R5" t="n">
-        <v>7246617</v>
+        <v>7246540</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,6 +1124,11 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1125,12 +1150,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Död gran</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Död gran</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1148,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119506911</v>
+        <v>119506747</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,34 +1189,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541171</v>
+        <v>541170</v>
       </c>
       <c r="R6" t="n">
-        <v>7246430</v>
+        <v>7246408</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,6 +1256,11 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1245,14 +1280,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>Stående, tunn</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies # Stående, tunn</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1270,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119506894</v>
+        <v>119506823</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>91005</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,25 +1312,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1310,10 +1340,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541231</v>
+        <v>541301</v>
       </c>
       <c r="R7" t="n">
-        <v>7246552</v>
+        <v>7246617</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1392,7 +1422,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119506788</v>
+        <v>119506746</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1428,7 +1458,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1437,10 +1467,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541330</v>
+        <v>541150</v>
       </c>
       <c r="R8" t="n">
-        <v>7246526</v>
+        <v>7246388</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,7 +1507,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Barksprätt, färska</t>
+          <t>Ringhack, äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1519,10 +1549,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119506758</v>
+        <v>119506728</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1535,39 +1565,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541244</v>
+        <v>541156</v>
       </c>
       <c r="R9" t="n">
-        <v>7246495</v>
+        <v>7246364</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1602,11 +1627,6 @@
           <t>2024-08-07</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, kåda rinnig</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1626,9 +1646,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Granlåga knäck</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga knäck</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1646,10 +1671,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119506905</v>
+        <v>119506790</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1662,34 +1687,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541343</v>
+        <v>541156</v>
       </c>
       <c r="R10" t="n">
-        <v>7246440</v>
+        <v>7246089</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1724,6 +1754,11 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Barksprätt, färska</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1743,14 +1778,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1768,7 +1798,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119506790</v>
+        <v>119506756</v>
       </c>
       <c r="B11" t="n">
         <v>57310</v>
@@ -1813,10 +1843,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541156</v>
+        <v>541300</v>
       </c>
       <c r="R11" t="n">
-        <v>7246089</v>
+        <v>7246546</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1853,7 +1883,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Barksprätt, färska</t>
+          <t>Ringhack, färska, rinnande kåda</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1895,10 +1925,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119506748</v>
+        <v>119506870</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1911,39 +1941,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541248</v>
+        <v>541220</v>
       </c>
       <c r="R12" t="n">
-        <v>7246485</v>
+        <v>7246538</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1980,7 +2005,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre</t>
+          <t>Fjolårets fruktkroppar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2002,9 +2027,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Död gran</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Död gran</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2022,7 +2052,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119506921</v>
+        <v>119506916</v>
       </c>
       <c r="B13" t="n">
         <v>78526</v>
@@ -2062,10 +2092,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541273</v>
+        <v>541318</v>
       </c>
       <c r="R13" t="n">
-        <v>7246560</v>
+        <v>7246426</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2098,6 +2128,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Flera träd</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2124,7 +2159,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119506767</v>
+        <v>119506740</v>
       </c>
       <c r="B14" t="n">
         <v>57310</v>
@@ -2160,7 +2195,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2169,10 +2204,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541165</v>
+        <v>541246</v>
       </c>
       <c r="R14" t="n">
-        <v>7246407</v>
+        <v>7246499</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2209,7 +2244,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, färska</t>
+          <t>Ringhack, äldre och även barksprätt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2251,10 +2286,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119506756</v>
+        <v>119506920</v>
       </c>
       <c r="B15" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2267,39 +2302,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541300</v>
+        <v>541219</v>
       </c>
       <c r="R15" t="n">
-        <v>7246546</v>
+        <v>7246495</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2334,11 +2364,6 @@
           <t>2024-08-07</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, rinnande kåda</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2347,21 +2372,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2378,7 +2388,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119506761</v>
+        <v>119506743</v>
       </c>
       <c r="B16" t="n">
         <v>57310</v>
@@ -2414,7 +2424,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2423,10 +2433,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541343</v>
+        <v>541283</v>
       </c>
       <c r="R16" t="n">
-        <v>7246497</v>
+        <v>7246547</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2463,7 +2473,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, färska</t>
+          <t>Ringhack, äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2505,10 +2515,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119506916</v>
+        <v>119506885</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2521,21 +2531,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2545,10 +2555,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541318</v>
+        <v>541178</v>
       </c>
       <c r="R17" t="n">
-        <v>7246426</v>
+        <v>7246374</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2583,11 +2593,6 @@
           <t>2024-08-07</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Flera träd</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2596,6 +2601,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>levande, stor gran</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies # levande, stor gran</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2612,10 +2637,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119506724</v>
+        <v>119506763</v>
       </c>
       <c r="B18" t="n">
-        <v>90905</v>
+        <v>57310</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2624,41 +2649,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541152</v>
+        <v>541120</v>
       </c>
       <c r="R18" t="n">
-        <v>7246375</v>
+        <v>7246108</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2695,7 +2722,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Kollekt</t>
+          <t>Ringhack, färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2704,7 +2731,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2738,10 +2764,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119506745</v>
+        <v>119506922</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2754,39 +2780,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541139</v>
+        <v>541267</v>
       </c>
       <c r="R19" t="n">
-        <v>7246098</v>
+        <v>7246600</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2821,11 +2842,6 @@
           <t>2024-08-07</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2834,21 +2850,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2865,10 +2866,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119506742</v>
+        <v>119506889</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2881,39 +2882,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541246</v>
+        <v>541232</v>
       </c>
       <c r="R20" t="n">
-        <v>7246498</v>
+        <v>7246564</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2948,11 +2944,6 @@
           <t>2024-08-07</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, 5 meter upp på stammen</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2972,9 +2963,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Granlåga, tunnare</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga, tunnare</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2992,7 +2988,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119506780</v>
+        <v>119506745</v>
       </c>
       <c r="B21" t="n">
         <v>57310</v>
@@ -3037,10 +3033,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541221</v>
+        <v>541139</v>
       </c>
       <c r="R21" t="n">
-        <v>7246540</v>
+        <v>7246098</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3077,7 +3073,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Barksprätt</t>
+          <t>Ringhack, äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3099,14 +3095,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>Död gran</t>
-        </is>
-      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies # Död gran</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3124,7 +3115,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119506743</v>
+        <v>119506789</v>
       </c>
       <c r="B22" t="n">
         <v>57310</v>
@@ -3160,7 +3151,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3169,10 +3160,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541283</v>
+        <v>541341</v>
       </c>
       <c r="R22" t="n">
-        <v>7246547</v>
+        <v>7246435</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3209,7 +3200,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack, äldre</t>
+          <t>Barksprätt, färska</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3251,7 +3242,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119506766</v>
+        <v>119506758</v>
       </c>
       <c r="B23" t="n">
         <v>57310</v>
@@ -3296,10 +3287,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541151</v>
+        <v>541244</v>
       </c>
       <c r="R23" t="n">
-        <v>7246341</v>
+        <v>7246495</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3336,7 +3327,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack, färska</t>
+          <t>Ringhack, färska, kåda rinnig</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3378,10 +3369,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119506781</v>
+        <v>119506811</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>79636</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3390,43 +3381,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541167</v>
+        <v>541313</v>
       </c>
       <c r="R24" t="n">
-        <v>7246427</v>
+        <v>7246548</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3461,11 +3447,6 @@
           <t>2024-08-07</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Barksprätt vid basen</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3477,17 +3458,17 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3505,7 +3486,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119506808</v>
+        <v>119506767</v>
       </c>
       <c r="B25" t="n">
         <v>57310</v>
@@ -3541,7 +3522,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3550,10 +3531,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541140</v>
+        <v>541165</v>
       </c>
       <c r="R25" t="n">
-        <v>7246303</v>
+        <v>7246407</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3590,7 +3571,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack på tall i myrkanten</t>
+          <t>Ringhack, färska</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3604,22 +3585,17 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>Ca 8 meter hög</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Ca 8 meter hög</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3637,10 +3613,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119506811</v>
+        <v>119506766</v>
       </c>
       <c r="B26" t="n">
-        <v>79636</v>
+        <v>57310</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3649,38 +3625,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541313</v>
+        <v>541151</v>
       </c>
       <c r="R26" t="n">
-        <v>7246548</v>
+        <v>7246341</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3715,6 +3696,11 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack, färska</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3726,17 +3712,17 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3754,10 +3740,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119506892</v>
+        <v>119506724</v>
       </c>
       <c r="B27" t="n">
-        <v>90580</v>
+        <v>90905</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3766,38 +3752,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>2062</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541125</v>
+        <v>541152</v>
       </c>
       <c r="R27" t="n">
-        <v>7246121</v>
+        <v>7246375</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3832,12 +3821,18 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Kollekt</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3851,14 +3846,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3876,7 +3866,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119506749</v>
+        <v>119506808</v>
       </c>
       <c r="B28" t="n">
         <v>57310</v>
@@ -3921,10 +3911,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541258</v>
+        <v>541140</v>
       </c>
       <c r="R28" t="n">
-        <v>7246630</v>
+        <v>7246303</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3961,7 +3951,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack, äldre</t>
+          <t>Ringhack på tall i myrkanten</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3975,17 +3965,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Ca 8 meter hög</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris # Ca 8 meter hög</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4003,7 +3998,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119506740</v>
+        <v>119506749</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -4048,10 +4043,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541246</v>
+        <v>541258</v>
       </c>
       <c r="R29" t="n">
-        <v>7246499</v>
+        <v>7246630</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4088,7 +4083,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, äldre och även barksprätt</t>
+          <t>Ringhack, äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4130,10 +4125,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119506904</v>
+        <v>119506788</v>
       </c>
       <c r="B30" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4146,34 +4141,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541286</v>
+        <v>541330</v>
       </c>
       <c r="R30" t="n">
-        <v>7246540</v>
+        <v>7246526</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4208,6 +4208,11 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Barksprätt, färska</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4227,14 +4232,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>Granhögstubbe, tunn</t>
-        </is>
-      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, tunn</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4252,10 +4252,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119506893</v>
+        <v>119506748</v>
       </c>
       <c r="B31" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4268,34 +4268,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541176</v>
+        <v>541248</v>
       </c>
       <c r="R31" t="n">
-        <v>7246371</v>
+        <v>7246485</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4330,6 +4335,11 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4349,14 +4359,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4374,10 +4379,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119506922</v>
+        <v>119506761</v>
       </c>
       <c r="B32" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4390,34 +4395,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541267</v>
+        <v>541343</v>
       </c>
       <c r="R32" t="n">
-        <v>7246600</v>
+        <v>7246497</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4452,6 +4462,11 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack, färska</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4460,6 +4475,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4476,10 +4506,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119506731</v>
+        <v>119506904</v>
       </c>
       <c r="B33" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4492,21 +4522,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4516,10 +4546,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541301</v>
+        <v>541286</v>
       </c>
       <c r="R33" t="n">
-        <v>7246617</v>
+        <v>7246540</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4575,12 +4605,12 @@
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>Granlåga knäck</t>
+          <t>Granhögstubbe, tunn</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäck</t>
+          <t>Picea abies # Granhögstubbe, tunn</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4598,7 +4628,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119506741</v>
+        <v>119506791</v>
       </c>
       <c r="B34" t="n">
         <v>57310</v>
@@ -4634,7 +4664,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4643,10 +4673,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541156</v>
+        <v>541172</v>
       </c>
       <c r="R34" t="n">
-        <v>7246381</v>
+        <v>7246349</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4683,7 +4713,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, äldre</t>
+          <t>Barksprätt, färska</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4705,14 +4735,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>Granstubbe, knäckt</t>
-        </is>
-      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies # Granstubbe, knäckt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4730,10 +4755,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119506870</v>
+        <v>119506781</v>
       </c>
       <c r="B35" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4746,34 +4771,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541220</v>
+        <v>541167</v>
       </c>
       <c r="R35" t="n">
-        <v>7246538</v>
+        <v>7246427</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4810,7 +4840,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Fjolårets fruktkroppar</t>
+          <t>Barksprätt vid basen</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4832,14 +4862,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL35" t="inlineStr">
-        <is>
-          <t>Död gran</t>
-        </is>
-      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Picea abies # Död gran</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4857,10 +4882,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119506728</v>
+        <v>119506742</v>
       </c>
       <c r="B36" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4873,34 +4898,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541156</v>
+        <v>541246</v>
       </c>
       <c r="R36" t="n">
-        <v>7246364</v>
+        <v>7246498</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4935,6 +4965,11 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, 5 meter upp på stammen</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4954,14 +4989,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL36" t="inlineStr">
-        <is>
-          <t>Granlåga knäck</t>
-        </is>
-      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäck</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4979,10 +5009,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119506920</v>
+        <v>119506731</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4995,21 +5025,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5019,10 +5049,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541219</v>
+        <v>541301</v>
       </c>
       <c r="R37" t="n">
-        <v>7246495</v>
+        <v>7246617</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5065,6 +5095,26 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>Granlåga knäck</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga knäck</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5081,10 +5131,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119506791</v>
+        <v>119506921</v>
       </c>
       <c r="B38" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5097,39 +5147,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541172</v>
+        <v>541273</v>
       </c>
       <c r="R38" t="n">
-        <v>7246349</v>
+        <v>7246560</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5164,11 +5209,6 @@
           <t>2024-08-07</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Barksprätt, färska</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5177,21 +5217,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5208,10 +5233,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119506763</v>
+        <v>119506894</v>
       </c>
       <c r="B39" t="n">
-        <v>57310</v>
+        <v>90580</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5224,39 +5249,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541120</v>
+        <v>541231</v>
       </c>
       <c r="R39" t="n">
-        <v>7246108</v>
+        <v>7246552</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5291,11 +5311,6 @@
           <t>2024-08-07</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack, färska</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5315,9 +5330,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5335,7 +5355,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119506746</v>
+        <v>119506741</v>
       </c>
       <c r="B40" t="n">
         <v>57310</v>
@@ -5380,10 +5400,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541150</v>
+        <v>541156</v>
       </c>
       <c r="R40" t="n">
-        <v>7246388</v>
+        <v>7246381</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5442,9 +5462,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>Granstubbe, knäckt</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granstubbe, knäckt</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5462,10 +5487,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119506747</v>
+        <v>119506917</v>
       </c>
       <c r="B41" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5478,39 +5503,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541170</v>
+        <v>541296</v>
       </c>
       <c r="R41" t="n">
-        <v>7246408</v>
+        <v>7246533</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5545,11 +5565,6 @@
           <t>2024-08-07</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5558,21 +5573,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5589,10 +5589,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119506888</v>
+        <v>119506918</v>
       </c>
       <c r="B42" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5605,21 +5605,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5632,7 +5632,7 @@
         <v>541357</v>
       </c>
       <c r="R42" t="n">
-        <v>7246528</v>
+        <v>7246504</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5675,26 +5675,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL42" t="inlineStr">
-        <is>
-          <t>Granlåga, tunnare</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga, tunnare</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5711,7 +5691,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119506889</v>
+        <v>119506905</v>
       </c>
       <c r="B43" t="n">
         <v>90580</v>
@@ -5751,10 +5731,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541232</v>
+        <v>541343</v>
       </c>
       <c r="R43" t="n">
-        <v>7246564</v>
+        <v>7246440</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5810,12 +5790,12 @@
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>Granlåga, tunnare</t>
+          <t>Granhögstubbe</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, tunnare</t>
+          <t>Picea abies # Granhögstubbe</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5833,10 +5813,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119506917</v>
+        <v>119506893</v>
       </c>
       <c r="B44" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5849,21 +5829,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5873,10 +5853,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541296</v>
+        <v>541176</v>
       </c>
       <c r="R44" t="n">
-        <v>7246533</v>
+        <v>7246371</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5919,6 +5899,26 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL44" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">

--- a/artfynd/A 28799-2024 artfynd.xlsx
+++ b/artfynd/A 28799-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5933,6 +5933,118 @@
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>122118157</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57365</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Matsdal, öst, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>541278</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7246392</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack äldre, söder kraftledningsgatan</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28799-2024 artfynd.xlsx
+++ b/artfynd/A 28799-2024 artfynd.xlsx
@@ -5938,7 +5938,7 @@
         <v>122118157</v>
       </c>
       <c r="B45" t="n">
-        <v>57365</v>
+        <v>57369</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>

--- a/artfynd/A 28799-2024 artfynd.xlsx
+++ b/artfynd/A 28799-2024 artfynd.xlsx
@@ -5938,7 +5938,7 @@
         <v>122118157</v>
       </c>
       <c r="B45" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>

--- a/artfynd/A 28799-2024 artfynd.xlsx
+++ b/artfynd/A 28799-2024 artfynd.xlsx
@@ -5953,11 +5953,6 @@
       <c r="E45" t="n">
         <v>100109</v>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>

--- a/artfynd/A 28799-2024 artfynd.xlsx
+++ b/artfynd/A 28799-2024 artfynd.xlsx
@@ -5938,7 +5938,7 @@
         <v>122118157</v>
       </c>
       <c r="B45" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5952,6 +5952,11 @@
       </c>
       <c r="E45" t="n">
         <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>

--- a/artfynd/A 28799-2024 artfynd.xlsx
+++ b/artfynd/A 28799-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119506892</v>
+        <v>119506780</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,34 +935,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541125</v>
+        <v>541221</v>
       </c>
       <c r="R4" t="n">
-        <v>7246121</v>
+        <v>7246540</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,6 +1002,11 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1018,12 +1028,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Död gran</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Död gran</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1041,7 +1051,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119506780</v>
+        <v>119506747</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1086,10 +1096,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541221</v>
+        <v>541170</v>
       </c>
       <c r="R5" t="n">
-        <v>7246540</v>
+        <v>7246408</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,7 +1136,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Barksprätt</t>
+          <t>Ringhack, äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,14 +1158,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>Död gran</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies # Död gran</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1173,10 +1178,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119506747</v>
+        <v>119506823</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>91005</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,43 +1190,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541170</v>
+        <v>541301</v>
       </c>
       <c r="R6" t="n">
-        <v>7246408</v>
+        <v>7246617</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,11 +1256,6 @@
           <t>2024-08-07</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1280,9 +1275,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119506823</v>
+        <v>119506746</v>
       </c>
       <c r="B7" t="n">
-        <v>91005</v>
+        <v>57310</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,38 +1312,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541301</v>
+        <v>541150</v>
       </c>
       <c r="R7" t="n">
-        <v>7246617</v>
+        <v>7246388</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1378,6 +1383,11 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1397,14 +1407,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1422,10 +1427,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119506746</v>
+        <v>119506728</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1438,39 +1443,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541150</v>
+        <v>541156</v>
       </c>
       <c r="R8" t="n">
-        <v>7246388</v>
+        <v>7246364</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1505,11 +1505,6 @@
           <t>2024-08-07</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1529,9 +1524,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Granlåga knäck</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga knäck</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1549,10 +1549,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119506728</v>
+        <v>119506756</v>
       </c>
       <c r="B9" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1565,34 +1565,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541156</v>
+        <v>541300</v>
       </c>
       <c r="R9" t="n">
-        <v>7246364</v>
+        <v>7246546</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1627,6 +1632,11 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, rinnande kåda</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1646,14 +1656,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>Granlåga knäck</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäck</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1671,10 +1676,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119506790</v>
+        <v>119506870</v>
       </c>
       <c r="B10" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1687,39 +1692,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541156</v>
+        <v>541220</v>
       </c>
       <c r="R10" t="n">
-        <v>7246089</v>
+        <v>7246538</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Barksprätt, färska</t>
+          <t>Fjolårets fruktkroppar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1778,9 +1778,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Död gran</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Död gran</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1798,10 +1803,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119506756</v>
+        <v>119506916</v>
       </c>
       <c r="B11" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1814,39 +1819,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541300</v>
+        <v>541318</v>
       </c>
       <c r="R11" t="n">
-        <v>7246546</v>
+        <v>7246426</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, färska, rinnande kåda</t>
+          <t>Flera träd</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1894,21 +1894,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1925,10 +1910,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119506870</v>
+        <v>119506740</v>
       </c>
       <c r="B12" t="n">
-        <v>90558</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1941,34 +1926,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541220</v>
+        <v>541246</v>
       </c>
       <c r="R12" t="n">
-        <v>7246538</v>
+        <v>7246499</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2005,7 +1995,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Fjolårets fruktkroppar</t>
+          <t>Ringhack, äldre och även barksprätt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2027,14 +2017,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Död gran</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies # Död gran</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2052,7 +2037,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119506916</v>
+        <v>119506920</v>
       </c>
       <c r="B13" t="n">
         <v>78526</v>
@@ -2092,10 +2077,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541318</v>
+        <v>541219</v>
       </c>
       <c r="R13" t="n">
-        <v>7246426</v>
+        <v>7246495</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2128,11 +2113,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Flera träd</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2159,7 +2139,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119506740</v>
+        <v>119506743</v>
       </c>
       <c r="B14" t="n">
         <v>57310</v>
@@ -2204,10 +2184,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541246</v>
+        <v>541283</v>
       </c>
       <c r="R14" t="n">
-        <v>7246499</v>
+        <v>7246547</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2244,7 +2224,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, äldre och även barksprätt</t>
+          <t>Ringhack, äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2286,10 +2266,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119506920</v>
+        <v>119506885</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2302,21 +2282,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2326,10 +2306,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541219</v>
+        <v>541178</v>
       </c>
       <c r="R15" t="n">
-        <v>7246495</v>
+        <v>7246374</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2372,6 +2352,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>levande, stor gran</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies # levande, stor gran</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2388,10 +2388,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119506743</v>
+        <v>119506922</v>
       </c>
       <c r="B16" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2404,39 +2404,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541283</v>
+        <v>541267</v>
       </c>
       <c r="R16" t="n">
-        <v>7246547</v>
+        <v>7246600</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2471,11 +2466,6 @@
           <t>2024-08-07</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2484,21 +2474,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2515,7 +2490,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119506885</v>
+        <v>119506889</v>
       </c>
       <c r="B17" t="n">
         <v>90580</v>
@@ -2555,10 +2530,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541178</v>
+        <v>541232</v>
       </c>
       <c r="R17" t="n">
-        <v>7246374</v>
+        <v>7246564</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2614,12 +2589,12 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>levande, stor gran</t>
+          <t>Granlåga, tunnare</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies # levande, stor gran</t>
+          <t>Picea abies # Granlåga, tunnare</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2637,7 +2612,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119506763</v>
+        <v>119506789</v>
       </c>
       <c r="B18" t="n">
         <v>57310</v>
@@ -2682,10 +2657,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541120</v>
+        <v>541341</v>
       </c>
       <c r="R18" t="n">
-        <v>7246108</v>
+        <v>7246435</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2722,7 +2697,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack, färska</t>
+          <t>Barksprätt, färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2764,10 +2739,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119506922</v>
+        <v>119506758</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2780,34 +2755,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541267</v>
+        <v>541244</v>
       </c>
       <c r="R19" t="n">
-        <v>7246600</v>
+        <v>7246495</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2842,6 +2822,11 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, kåda rinnig</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2850,6 +2835,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2866,10 +2866,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119506889</v>
+        <v>119506811</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>79636</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2878,25 +2878,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2906,10 +2906,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541232</v>
+        <v>541313</v>
       </c>
       <c r="R20" t="n">
-        <v>7246564</v>
+        <v>7246548</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2955,22 +2955,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>Granlåga, tunnare</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, tunnare</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2988,7 +2983,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119506745</v>
+        <v>119506767</v>
       </c>
       <c r="B21" t="n">
         <v>57310</v>
@@ -3024,7 +3019,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3033,10 +3028,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541139</v>
+        <v>541165</v>
       </c>
       <c r="R21" t="n">
-        <v>7246098</v>
+        <v>7246407</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3073,7 +3068,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, äldre</t>
+          <t>Ringhack, färska</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3115,10 +3110,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119506789</v>
+        <v>119506724</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>90905</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3127,43 +3122,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541341</v>
+        <v>541152</v>
       </c>
       <c r="R22" t="n">
-        <v>7246435</v>
+        <v>7246375</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3200,7 +3193,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Barksprätt, färska</t>
+          <t>Kollekt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3209,6 +3202,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3242,7 +3236,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119506758</v>
+        <v>119506749</v>
       </c>
       <c r="B23" t="n">
         <v>57310</v>
@@ -3278,7 +3272,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3287,10 +3281,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541244</v>
+        <v>541258</v>
       </c>
       <c r="R23" t="n">
-        <v>7246495</v>
+        <v>7246630</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3327,7 +3321,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack, färska, kåda rinnig</t>
+          <t>Ringhack, äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3369,10 +3363,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119506811</v>
+        <v>119506788</v>
       </c>
       <c r="B24" t="n">
-        <v>79636</v>
+        <v>57310</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3381,38 +3375,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541313</v>
+        <v>541330</v>
       </c>
       <c r="R24" t="n">
-        <v>7246548</v>
+        <v>7246526</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3447,6 +3446,11 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Barksprätt, färska</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3458,17 +3462,17 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3486,7 +3490,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119506767</v>
+        <v>119506748</v>
       </c>
       <c r="B25" t="n">
         <v>57310</v>
@@ -3522,7 +3526,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3531,10 +3535,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541165</v>
+        <v>541248</v>
       </c>
       <c r="R25" t="n">
-        <v>7246407</v>
+        <v>7246485</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3571,7 +3575,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, färska</t>
+          <t>Ringhack, äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3613,7 +3617,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119506766</v>
+        <v>119506761</v>
       </c>
       <c r="B26" t="n">
         <v>57310</v>
@@ -3658,10 +3662,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541151</v>
+        <v>541343</v>
       </c>
       <c r="R26" t="n">
-        <v>7246341</v>
+        <v>7246497</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3740,10 +3744,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119506724</v>
+        <v>119506904</v>
       </c>
       <c r="B27" t="n">
-        <v>90905</v>
+        <v>90580</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3752,41 +3756,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2062</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541152</v>
+        <v>541286</v>
       </c>
       <c r="R27" t="n">
-        <v>7246375</v>
+        <v>7246540</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3821,18 +3822,12 @@
           <t>2024-08-07</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3846,9 +3841,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>Granhögstubbe, tunn</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granhögstubbe, tunn</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3866,7 +3866,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119506808</v>
+        <v>119506791</v>
       </c>
       <c r="B28" t="n">
         <v>57310</v>
@@ -3902,7 +3902,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541140</v>
+        <v>541172</v>
       </c>
       <c r="R28" t="n">
-        <v>7246303</v>
+        <v>7246349</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack på tall i myrkanten</t>
+          <t>Barksprätt, färska</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3965,22 +3965,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>Ca 8 meter hög</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Ca 8 meter hög</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3998,7 +3993,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119506749</v>
+        <v>119506781</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -4043,10 +4038,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541258</v>
+        <v>541167</v>
       </c>
       <c r="R29" t="n">
-        <v>7246630</v>
+        <v>7246427</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4083,7 +4078,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, äldre</t>
+          <t>Barksprätt vid basen</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4125,7 +4120,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119506788</v>
+        <v>119506742</v>
       </c>
       <c r="B30" t="n">
         <v>57310</v>
@@ -4161,7 +4156,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4170,10 +4165,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541330</v>
+        <v>541246</v>
       </c>
       <c r="R30" t="n">
-        <v>7246526</v>
+        <v>7246498</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4210,7 +4205,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Barksprätt, färska</t>
+          <t>Ringhack, äldre, 5 meter upp på stammen</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4252,10 +4247,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119506748</v>
+        <v>119506731</v>
       </c>
       <c r="B31" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4268,39 +4263,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541248</v>
+        <v>541301</v>
       </c>
       <c r="R31" t="n">
-        <v>7246485</v>
+        <v>7246617</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4335,11 +4325,6 @@
           <t>2024-08-07</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4359,9 +4344,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>Granlåga knäck</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga knäck</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4379,10 +4369,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119506761</v>
+        <v>119506921</v>
       </c>
       <c r="B32" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4395,39 +4385,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541343</v>
+        <v>541273</v>
       </c>
       <c r="R32" t="n">
-        <v>7246497</v>
+        <v>7246560</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4462,11 +4447,6 @@
           <t>2024-08-07</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack, färska</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4475,21 +4455,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4506,7 +4471,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119506904</v>
+        <v>119506894</v>
       </c>
       <c r="B33" t="n">
         <v>90580</v>
@@ -4546,10 +4511,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541286</v>
+        <v>541231</v>
       </c>
       <c r="R33" t="n">
-        <v>7246540</v>
+        <v>7246552</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4605,12 +4570,12 @@
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>Granhögstubbe, tunn</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, tunn</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4628,7 +4593,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119506791</v>
+        <v>119506741</v>
       </c>
       <c r="B34" t="n">
         <v>57310</v>
@@ -4664,7 +4629,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4673,10 +4638,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541172</v>
+        <v>541156</v>
       </c>
       <c r="R34" t="n">
-        <v>7246349</v>
+        <v>7246381</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4713,7 +4678,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Barksprätt, färska</t>
+          <t>Ringhack, äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4735,9 +4700,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>Granstubbe, knäckt</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granstubbe, knäckt</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4755,10 +4725,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119506781</v>
+        <v>119506917</v>
       </c>
       <c r="B35" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4771,39 +4741,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541167</v>
+        <v>541296</v>
       </c>
       <c r="R35" t="n">
-        <v>7246427</v>
+        <v>7246533</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4838,11 +4803,6 @@
           <t>2024-08-07</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Barksprätt vid basen</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4851,21 +4811,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4882,10 +4827,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119506742</v>
+        <v>119506918</v>
       </c>
       <c r="B36" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4898,39 +4843,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541246</v>
+        <v>541357</v>
       </c>
       <c r="R36" t="n">
-        <v>7246498</v>
+        <v>7246504</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4965,11 +4905,6 @@
           <t>2024-08-07</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, 5 meter upp på stammen</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4978,21 +4913,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5009,10 +4929,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119506731</v>
+        <v>119506905</v>
       </c>
       <c r="B37" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5025,21 +4945,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5049,10 +4969,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541301</v>
+        <v>541343</v>
       </c>
       <c r="R37" t="n">
-        <v>7246617</v>
+        <v>7246440</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5108,12 +5028,12 @@
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>Granlåga knäck</t>
+          <t>Granhögstubbe</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäck</t>
+          <t>Picea abies # Granhögstubbe</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5131,10 +5051,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119506921</v>
+        <v>119506893</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5147,21 +5067,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5171,10 +5091,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541273</v>
+        <v>541176</v>
       </c>
       <c r="R38" t="n">
-        <v>7246560</v>
+        <v>7246371</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5217,6 +5137,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5233,10 +5173,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119506894</v>
+        <v>122118157</v>
       </c>
       <c r="B39" t="n">
-        <v>90580</v>
+        <v>57383</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5249,34 +5189,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Matsdal, Ås lm</t>
+          <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541231</v>
+        <v>541278</v>
       </c>
       <c r="R39" t="n">
-        <v>7246552</v>
+        <v>7246392</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5303,12 +5248,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre, söder kraftledningsgatan</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5319,26 +5269,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL39" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5352,698 +5282,6 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>119506741</v>
-      </c>
-      <c r="B40" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Matsdal, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>541156</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7246381</v>
-      </c>
-      <c r="S40" t="n">
-        <v>10</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL40" t="inlineStr">
-        <is>
-          <t>Granstubbe, knäckt</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Picea abies # Granstubbe, knäckt</t>
-        </is>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>119506917</v>
-      </c>
-      <c r="B41" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Matsdal, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>541296</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7246533</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>119506918</v>
-      </c>
-      <c r="B42" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Matsdal, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>541357</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7246504</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>119506905</v>
-      </c>
-      <c r="B43" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Matsdal, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>541343</v>
-      </c>
-      <c r="R43" t="n">
-        <v>7246440</v>
-      </c>
-      <c r="S43" t="n">
-        <v>10</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>119506893</v>
-      </c>
-      <c r="B44" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Matsdal, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>541176</v>
-      </c>
-      <c r="R44" t="n">
-        <v>7246371</v>
-      </c>
-      <c r="S44" t="n">
-        <v>10</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL44" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>122118157</v>
-      </c>
-      <c r="B45" t="n">
-        <v>57383</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Matsdal, öst, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>541278</v>
-      </c>
-      <c r="R45" t="n">
-        <v>7246392</v>
-      </c>
-      <c r="S45" t="n">
-        <v>10</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2024-12-31</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2024-12-31</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack äldre, söder kraftledningsgatan</t>
-        </is>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28799-2024 artfynd.xlsx
+++ b/artfynd/A 28799-2024 artfynd.xlsx
@@ -1763,7 +1763,7 @@
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="b">
         <v>0</v>
@@ -3200,7 +3200,7 @@
         <v>0</v>
       </c>
       <c r="AE22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">

--- a/artfynd/A 28799-2024 artfynd.xlsx
+++ b/artfynd/A 28799-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119506911</v>
+        <v>119506870</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541171</v>
+        <v>541220</v>
       </c>
       <c r="R2" t="n">
-        <v>7246430</v>
+        <v>7246538</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,11 +748,16 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -774,12 +774,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Stående, tunn</t>
+          <t>Död gran</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies # Stående, tunn</t>
+          <t>Picea abies # Död gran</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,15 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119506888</v>
+        <v>119506728</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541357</v>
+        <v>541156</v>
       </c>
       <c r="R3" t="n">
-        <v>7246528</v>
+        <v>7246364</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,12 +891,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Granlåga, tunnare</t>
+          <t>Granlåga knäck</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, tunnare</t>
+          <t>Picea abies # Granlåga knäck</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,15 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119506780</v>
+        <v>119506731</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,39 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541221</v>
+        <v>541301</v>
       </c>
       <c r="R4" t="n">
-        <v>7246540</v>
+        <v>7246617</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,11 +987,6 @@
           <t>2024-08-07</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1028,12 +1008,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Död gran</t>
+          <t>Granlåga knäck</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies # Död gran</t>
+          <t>Picea abies # Granlåga knäck</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1051,15 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119506747</v>
+        <v>119506823</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,39 +1042,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541170</v>
+        <v>541301</v>
       </c>
       <c r="R5" t="n">
-        <v>7246408</v>
+        <v>7246617</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1134,11 +1104,6 @@
           <t>2024-08-07</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1158,9 +1123,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1178,15 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119506823</v>
+        <v>119506916</v>
       </c>
       <c r="B6" t="n">
-        <v>91005</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,21 +1159,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1218,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541301</v>
+        <v>541318</v>
       </c>
       <c r="R6" t="n">
-        <v>7246617</v>
+        <v>7246426</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,6 +1221,11 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera träd</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1264,26 +1234,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1300,55 +1250,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119506746</v>
+        <v>119506917</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>541150</v>
+        <v>541296</v>
       </c>
       <c r="R7" t="n">
-        <v>7246388</v>
+        <v>7246533</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1383,11 +1323,6 @@
           <t>2024-08-07</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1396,21 +1331,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1427,37 +1347,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119506728</v>
+        <v>119506918</v>
       </c>
       <c r="B8" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1467,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541156</v>
+        <v>541357</v>
       </c>
       <c r="R8" t="n">
-        <v>7246364</v>
+        <v>7246504</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1513,26 +1428,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Granlåga knäck</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga knäck</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1549,55 +1444,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119506756</v>
+        <v>119506920</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541300</v>
+        <v>541219</v>
       </c>
       <c r="R9" t="n">
-        <v>7246546</v>
+        <v>7246495</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1632,11 +1517,6 @@
           <t>2024-08-07</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, rinnande kåda</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1645,21 +1525,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1676,37 +1541,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119506870</v>
+        <v>119506921</v>
       </c>
       <c r="B10" t="n">
-        <v>90558</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1716,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541220</v>
+        <v>541273</v>
       </c>
       <c r="R10" t="n">
-        <v>7246538</v>
+        <v>7246560</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1754,39 +1614,14 @@
           <t>2024-08-07</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>Död gran</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies # Död gran</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1803,19 +1638,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119506916</v>
+        <v>119506922</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1843,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541318</v>
+        <v>541267</v>
       </c>
       <c r="R11" t="n">
-        <v>7246426</v>
+        <v>7246600</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1879,11 +1709,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Flera träd</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1910,55 +1735,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119506740</v>
+        <v>119506811</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541246</v>
+        <v>541313</v>
       </c>
       <c r="R12" t="n">
-        <v>7246499</v>
+        <v>7246548</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1993,11 +1808,6 @@
           <t>2024-08-07</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre och även barksprätt</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2009,17 +1819,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2037,15 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119506920</v>
+        <v>119506740</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2053,34 +1858,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541219</v>
+        <v>541246</v>
       </c>
       <c r="R13" t="n">
-        <v>7246495</v>
+        <v>7246499</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2115,6 +1925,11 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre och även barksprätt</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2123,6 +1938,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2139,15 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119506743</v>
+        <v>119506741</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2184,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541283</v>
+        <v>541156</v>
       </c>
       <c r="R14" t="n">
-        <v>7246547</v>
+        <v>7246381</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2246,9 +2071,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Granstubbe, knäckt</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granstubbe, knäckt</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2266,15 +2096,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119506885</v>
+        <v>119506742</v>
       </c>
       <c r="B15" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2282,34 +2107,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541178</v>
+        <v>541246</v>
       </c>
       <c r="R15" t="n">
-        <v>7246374</v>
+        <v>7246498</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2344,6 +2174,11 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, 5 meter upp på stammen</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2363,14 +2198,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>levande, stor gran</t>
-        </is>
-      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies # levande, stor gran</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2388,15 +2218,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119506922</v>
+        <v>119506743</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2404,34 +2229,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541267</v>
+        <v>541283</v>
       </c>
       <c r="R16" t="n">
-        <v>7246600</v>
+        <v>7246547</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2466,6 +2296,11 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2474,6 +2309,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2490,15 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119506889</v>
+        <v>119506746</v>
       </c>
       <c r="B17" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2506,34 +2351,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541232</v>
+        <v>541150</v>
       </c>
       <c r="R17" t="n">
-        <v>7246564</v>
+        <v>7246388</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2568,6 +2418,11 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2587,14 +2442,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>Granlåga, tunnare</t>
-        </is>
-      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, tunnare</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2612,15 +2462,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119506789</v>
+        <v>119506747</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2648,7 +2493,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2657,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541341</v>
+        <v>541170</v>
       </c>
       <c r="R18" t="n">
-        <v>7246435</v>
+        <v>7246408</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2697,7 +2542,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Barksprätt, färska</t>
+          <t>Ringhack, äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2739,15 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119506758</v>
+        <v>119506748</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2775,7 +2615,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2784,10 +2624,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541244</v>
+        <v>541248</v>
       </c>
       <c r="R19" t="n">
-        <v>7246495</v>
+        <v>7246485</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2824,7 +2664,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack, färska, kåda rinnig</t>
+          <t>Ringhack, äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2866,50 +2706,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119506811</v>
+        <v>119506749</v>
       </c>
       <c r="B20" t="n">
-        <v>79636</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541313</v>
+        <v>541258</v>
       </c>
       <c r="R20" t="n">
-        <v>7246548</v>
+        <v>7246630</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2944,6 +2784,11 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2955,17 +2800,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2983,15 +2828,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119506767</v>
+        <v>119506756</v>
       </c>
       <c r="B21" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3028,10 +2868,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541165</v>
+        <v>541300</v>
       </c>
       <c r="R21" t="n">
-        <v>7246407</v>
+        <v>7246546</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3068,7 +2908,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, färska</t>
+          <t>Ringhack, färska, rinnande kåda</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3110,53 +2950,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119506724</v>
+        <v>119506758</v>
       </c>
       <c r="B22" t="n">
-        <v>90905</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541152</v>
+        <v>541244</v>
       </c>
       <c r="R22" t="n">
-        <v>7246375</v>
+        <v>7246495</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3193,16 +3030,15 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Kollekt</t>
+          <t>Ringhack, färska, kåda rinnig</t>
         </is>
       </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF22" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3236,15 +3072,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119506749</v>
+        <v>119506761</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3272,7 +3103,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3281,10 +3112,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541258</v>
+        <v>541343</v>
       </c>
       <c r="R23" t="n">
-        <v>7246630</v>
+        <v>7246497</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3321,7 +3152,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack, äldre</t>
+          <t>Ringhack, färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3363,15 +3194,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119506788</v>
+        <v>119506765</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3408,10 +3234,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541330</v>
+        <v>541148</v>
       </c>
       <c r="R24" t="n">
-        <v>7246526</v>
+        <v>7246341</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3448,7 +3274,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Barksprätt, färska</t>
+          <t>Ringhack, färska</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3490,15 +3316,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119506748</v>
+        <v>119506766</v>
       </c>
       <c r="B25" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3526,7 +3347,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3535,10 +3356,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541248</v>
+        <v>541151</v>
       </c>
       <c r="R25" t="n">
-        <v>7246485</v>
+        <v>7246341</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3575,7 +3396,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre</t>
+          <t>Ringhack, färska</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3617,15 +3438,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119506761</v>
+        <v>119506767</v>
       </c>
       <c r="B26" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3662,10 +3478,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541343</v>
+        <v>541165</v>
       </c>
       <c r="R26" t="n">
-        <v>7246497</v>
+        <v>7246407</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3744,15 +3560,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119506904</v>
+        <v>119506780</v>
       </c>
       <c r="B27" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3760,31 +3571,36 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541286</v>
+        <v>541221</v>
       </c>
       <c r="R27" t="n">
         <v>7246540</v>
@@ -3822,6 +3638,11 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3843,12 +3664,12 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>Granhögstubbe, tunn</t>
+          <t>Död gran</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, tunn</t>
+          <t>Picea abies # Död gran</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3866,15 +3687,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119506791</v>
+        <v>119506781</v>
       </c>
       <c r="B28" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3902,7 +3718,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3911,10 +3727,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541172</v>
+        <v>541167</v>
       </c>
       <c r="R28" t="n">
-        <v>7246349</v>
+        <v>7246427</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3951,7 +3767,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Barksprätt, färska</t>
+          <t>Barksprätt vid basen</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3993,15 +3809,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119506781</v>
+        <v>119506788</v>
       </c>
       <c r="B29" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4029,7 +3840,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4038,10 +3849,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541167</v>
+        <v>541330</v>
       </c>
       <c r="R29" t="n">
-        <v>7246427</v>
+        <v>7246526</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4078,7 +3889,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Barksprätt vid basen</t>
+          <t>Barksprätt, färska</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4120,15 +3931,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119506742</v>
+        <v>119506789</v>
       </c>
       <c r="B30" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4156,7 +3962,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4165,10 +3971,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541246</v>
+        <v>541341</v>
       </c>
       <c r="R30" t="n">
-        <v>7246498</v>
+        <v>7246435</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4205,7 +4011,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, 5 meter upp på stammen</t>
+          <t>Barksprätt, färska</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4247,15 +4053,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119506731</v>
+        <v>119506791</v>
       </c>
       <c r="B31" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4263,34 +4064,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541301</v>
+        <v>541172</v>
       </c>
       <c r="R31" t="n">
-        <v>7246617</v>
+        <v>7246349</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4325,6 +4131,11 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Barksprätt, färska</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4344,14 +4155,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>Granlåga knäck</t>
-        </is>
-      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäck</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4369,15 +4175,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119506921</v>
+        <v>122118157</v>
       </c>
       <c r="B32" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4385,34 +4186,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Matsdal, Ås lm</t>
+          <t>Matsdal, öst, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541273</v>
+        <v>541278</v>
       </c>
       <c r="R32" t="n">
-        <v>7246560</v>
+        <v>7246392</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4439,12 +4245,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack äldre, söder kraftledningsgatan</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4471,50 +4282,43 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119506894</v>
+        <v>119506724</v>
       </c>
       <c r="B33" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92285</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6331024</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis delicata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Miettinen &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Matsdal, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541231</v>
+        <v>541152</v>
       </c>
       <c r="R33" t="n">
-        <v>7246552</v>
+        <v>7246375</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4549,12 +4353,18 @@
           <t>2024-08-07</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Kollekt Artbestämnd via mikroskopering</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4568,14 +4378,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4590,698 +4395,6 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>119506741</v>
-      </c>
-      <c r="B34" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Matsdal, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>541156</v>
-      </c>
-      <c r="R34" t="n">
-        <v>7246381</v>
-      </c>
-      <c r="S34" t="n">
-        <v>10</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>Granstubbe, knäckt</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies # Granstubbe, knäckt</t>
-        </is>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>119506917</v>
-      </c>
-      <c r="B35" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Matsdal, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>541296</v>
-      </c>
-      <c r="R35" t="n">
-        <v>7246533</v>
-      </c>
-      <c r="S35" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>119506918</v>
-      </c>
-      <c r="B36" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Matsdal, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>541357</v>
-      </c>
-      <c r="R36" t="n">
-        <v>7246504</v>
-      </c>
-      <c r="S36" t="n">
-        <v>10</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>119506905</v>
-      </c>
-      <c r="B37" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Matsdal, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>541343</v>
-      </c>
-      <c r="R37" t="n">
-        <v>7246440</v>
-      </c>
-      <c r="S37" t="n">
-        <v>10</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL37" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>119506893</v>
-      </c>
-      <c r="B38" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Matsdal, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>541176</v>
-      </c>
-      <c r="R38" t="n">
-        <v>7246371</v>
-      </c>
-      <c r="S38" t="n">
-        <v>10</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2024-08-07</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL38" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>122118157</v>
-      </c>
-      <c r="B39" t="n">
-        <v>57383</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Matsdal, öst, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>541278</v>
-      </c>
-      <c r="R39" t="n">
-        <v>7246392</v>
-      </c>
-      <c r="S39" t="n">
-        <v>10</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2024-12-31</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2024-12-31</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack äldre, söder kraftledningsgatan</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Roger Olofsson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
